--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,7 +713,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -747,32 +747,51 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UwJevjpg</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -780,43 +799,77 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scott g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -824,47 +877,77 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C2sV0kf7</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>U3POrPvM</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>zuJM7XDg</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>x6CvOHH9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -872,21 +955,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>x6CvOHH9</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>U3POrPvM</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -895,15 +982,19 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -911,21 +1002,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -936,18 +1027,29 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -958,57 +1060,55 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1019,18 +1119,29 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1039,7 +1150,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1047,94 +1158,84 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1145,7 +1246,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1154,7 +1255,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tMUvLt7h</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1162,7 +1263,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1173,7 +1274,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1184,7 +1285,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1193,7 +1294,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>phM8NElP</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1201,7 +1302,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1212,24 +1313,29 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1243,7 +1349,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1255,7 +1361,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1264,7 +1370,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1272,24 +1378,173 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t xml:space="preserve">bell j 
   eng </t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>n94TZqsm</t>
         </is>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,21 +713,16 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -739,7 +734,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -747,51 +742,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>hUGEt9yf</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MBpIn2MH</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -799,77 +775,43 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>lhUKMQZu</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">scott g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -877,77 +819,47 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">smith j 
   eng </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>zuJM7XDg</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>x6CvOHH9</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -955,25 +867,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>x6CvOHH9</t>
-        </is>
-      </c>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -982,19 +890,15 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1002,21 +906,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">langford o 
   eng </t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UwJevjpg</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1027,29 +931,18 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1060,55 +953,57 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1119,29 +1014,18 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1150,7 +1034,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1158,84 +1042,94 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1246,7 +1140,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1255,7 +1149,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1263,7 +1157,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1274,7 +1168,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1285,7 +1179,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1294,7 +1188,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1302,7 +1196,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1313,29 +1207,24 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1349,7 +1238,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1361,7 +1250,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1370,7 +1259,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1378,173 +1267,24 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="inlineStr">
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t xml:space="preserve">bell j 
   eng </t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>n94TZqsm</t>
         </is>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,8 +669,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,8 +721,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -973,83 +973,73 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1060,44 +1050,44 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1108,79 +1098,79 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1191,79 +1181,85 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1274,18 +1270,24 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1294,7 +1296,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>IuMTL627</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1302,18 +1304,33 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1321,64 +1338,53 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t xml:space="preserve">davies a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6wEAqBAE</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MsDWbjnD</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1389,35 +1395,35 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1428,125 +1434,114 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6wEAqBAE</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>1</v>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>8tPSZqtA</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bell j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>n94TZqsm</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,33 +453,28 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">donohue m 
-  eng </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +482,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +508,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +534,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">kitchen a 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +560,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,13 +586,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -609,7 +604,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +612,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,259 +638,259 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">gillett j 
   aus </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>zuJM7XDg</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AeRSxQrK</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U5cORazJ</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>hUGEt9yf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MBpIn2MH</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>lhUKMQZu</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">scott g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>IoJ2QpOs</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2g67Vsyf</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -903,25 +898,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -929,25 +924,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>x6CvOHH9</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -955,25 +950,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>x6CvOHH9</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -981,32 +976,51 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>lYgfxNV9</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>dKVYSSZa</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>dUjtW2Fr</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1014,43 +1028,77 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>tMOy79y1</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>pA2vPxeA</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>joDBK9gn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>UXQtpeyg</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>UsklUtpe</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1058,47 +1106,77 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
+          <t xml:space="preserve">corlett m 
   eng </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IPNnvzM7</t>
+          <t>thRJMAq0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>lYgfxNV9</t>
+          <t>Sx94bg0H</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>Sh9BS8ig</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1106,38 +1184,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">webb d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>IuMTL627</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>EkqxE9x0</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OEy2L7Zo</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>dAfPwfHi</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1145,60 +1236,103 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t xml:space="preserve">stockbridge s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>pSZhI8SM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oldham s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>v9wEyhMe</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SGvTSGmc</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>dY0SOQjI</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">martin s 
+  eng </t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>zLZktkzH</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>dtwAbyJ5</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>hO8aNYWA</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1206,105 +1340,181 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">webb d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t xml:space="preserve">simpson s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>pQTmYFAh</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nield t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>vDA9yPiL</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hicks c 
+  eng </t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6watkf6m</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">herczeg a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EqN1jJFK</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>bZDu1Nqp</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>WQF2UUMt</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bourne d 
+  eng </t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IuMTL627</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>65pf39vc</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>zJCJQnM5</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mather s 
+  eng </t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IuMTL627</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>YTxm48Ng</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>C2z7zmRI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>QkntzCGG</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1312,25 +1522,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">busby j 
+          <t xml:space="preserve">doughty l 
   eng </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>IPNnvzM7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>rkazN4LU</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1338,210 +1548,96 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">davies a 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6wEAqBAE</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pYaUUJs1</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>ddFjPf2b</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkinson b 
+  eng </t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>r597nj0B</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>6wEAqBAE</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>IPNnvzM7</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salisbury m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,13 +461,13 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">donohue m 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -519,19 +519,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,233 +643,233 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">gillett j 
   aus </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>zuJM7XDg</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AeRSxQrK</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U5cORazJ</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>hUGEt9yf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kitchen a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MBpIn2MH</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>lhUKMQZu</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">scott g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>IoJ2QpOs</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -877,25 +877,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -903,25 +903,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -929,25 +929,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>x6CvOHH9</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -955,25 +955,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>x6CvOHH9</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>rRQ6H30k</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -981,32 +981,51 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t xml:space="preserve">nield t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>lYgfxNV9</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>tMOy79y1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>MFnpCm7C</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1014,43 +1033,77 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t xml:space="preserve">madley r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>joDBK9gn</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>pA2vPxeA</t>
+          <t>phM8NElP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corlett m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sx94bg0H</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkinson b 
+  eng </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>r597nj0B</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>Sh9BS8ig</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1058,47 +1111,77 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IPNnvzM7</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>lYgfxNV9</t>
+          <t>IuMTL627</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stockbridge s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oldham s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>v9wEyhMe</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>jiUEFsV1</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1106,38 +1189,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">webb d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SGvTSGmc</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>dY0SOQjI</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">martin s 
+  eng </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OEy2L7Zo</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>zLZktkzH</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>dtwAbyJ5</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>hO8aNYWA</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1145,60 +1241,103 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t xml:space="preserve">simpson s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>pQTmYFAh</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hicks c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>6watkf6m</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>Q9rcSKE7</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">herczeg a 
+  eng </t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>EqN1jJFK</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>bZDu1Nqp</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>zJCJQnM5</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1206,105 +1345,181 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">webb d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t xml:space="preserve">mather s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>YTxm48Ng</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>C2z7zmRI</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doughty l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>Wn71woN8</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>UXQtpeyg</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salisbury m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>U32wGjPp</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IuMTL627</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>dKVYSSZa</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>hGzqjO6E</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IuMTL627</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>OrHrRGXo</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1312,25 +1527,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">busby j 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>MiVxbVgA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>WQF2UUMt</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1338,210 +1553,70 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">davies a 
+          <t xml:space="preserve">bourne d 
   eng </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6wEAqBAE</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pYaUUJs1</t>
+          <t>65pf39vc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>rkazN4LU</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>6wEAqBAE</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>IPNnvzM7</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -459,13 +454,12 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>GxXzVQFQ</t>
         </is>
@@ -480,13 +474,12 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
@@ -501,13 +494,12 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
         </is>
@@ -522,13 +514,12 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>lnG1OUjk</t>
         </is>
@@ -543,13 +534,12 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>xpALVpwq</t>
         </is>
@@ -564,13 +554,12 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
         </is>
@@ -585,338 +574,14 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>4rSZHs2M</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ERWFdKZh</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8QPOfb45</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>x6HuiG3U</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,67 +453,70 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +524,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t xml:space="preserve">pawson c 
+  eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +550,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t xml:space="preserve">barrott s 
+  eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,19 +576,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t xml:space="preserve">oliver m 
+  eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -576,12 +602,174 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>joAFj9hO</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,70 +453,85 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -524,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -550,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -576,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -602,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">allison s 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -628,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -654,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">taylor a 
+  eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -680,96 +695,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">allison s 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,254 +459,412 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>COqtASrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linington j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2L1wFbM5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Uu6L6Igl</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">howard p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>8QPOfb45</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>x6HuiG3U</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attwell s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,418 +448,60 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>COqtASrJ</t>
+          <t>thRJMAq0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MiVxbVgA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>zHJOSLsG</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>YuNX1zGT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>thRJMAq0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>va62Pxqi</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2kGeEq1e</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>OEy2L7Zo</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2TvL16Hk</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">linington j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>beYTapn2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith l 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2L1wFbM5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jkLFNmv9</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Uu6L6Igl</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AiyHLR8L</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>tzSnG5Wr</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">howard p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Wplk7SgS</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bell j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>pSZhI8SM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AVat9lPF</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">england d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t xml:space="preserve">taylor a 
+  eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>thRJMAq0</t>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t xml:space="preserve">smith l 
+  eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,12 +513,200 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>QHesBmSQ</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,6 +710,266 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,27 +453,28 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>d8abY4hR</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,12 +482,476 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>IoJ2QpOs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -459,13 +454,12 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
         </is>
@@ -482,16 +476,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
@@ -508,16 +496,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
@@ -534,16 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>vBIoDoo1</t>
         </is>
@@ -560,16 +536,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
         </is>
@@ -586,16 +556,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
         </is>
@@ -612,16 +576,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
@@ -638,16 +596,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
-  eng </t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -662,13 +614,12 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>IoJ2QpOs</t>
         </is>
@@ -683,275 +634,14 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>lAbHYaQM</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>8MkyzwoT</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>GhdgPLWA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>l6f1Na1N</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attwell s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>8MkyzwoT</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t xml:space="preserve">oliver m 
+  eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>GhdgPLWA</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,12 +487,486 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>IoJ2QpOs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -461,18 +456,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
     </row>
@@ -487,18 +476,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">england d 
-  eng </t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>
@@ -513,18 +496,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
     </row>
@@ -539,16 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>IoJ2QpOs</t>
         </is>
@@ -565,16 +536,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -591,16 +556,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
@@ -617,18 +576,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
     </row>
@@ -643,18 +596,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
@@ -669,302 +616,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>r3Wq3yFF</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>SQM1jbV9</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bFdtqGNq</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YXAOeg7k</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>tbEWgXy2</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>d6dJHzU8</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allison s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>l0Zi1FqS</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ltBAlx0M</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8MkyzwoT</t>
+          <t>KnvLwLo4</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GhdgPLWA</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>l6f1Na1N</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,132 +496,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,60 +453,366 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>r3Wq3yFF</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>SQM1jbV9</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>bFdtqGNq</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>lnG1OUjk</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r3Wq3yFF</t>
+          <t>ltBAlx0M</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,19 +483,19 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,166 +504,201 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YXAOeg7k</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbEWgXy2</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d6dJHzU8</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>zHJOSLsG</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -671,25 +706,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -697,122 +732,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
           <t>QHesBmSQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,70 +453,85 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -524,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -550,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -576,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -602,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -634,19 +649,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -654,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -680,25 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -706,25 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -732,18 +747,226 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>CznGurCt</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
@@ -485,12 +480,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
@@ -511,12 +501,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>joAFj9hO</t>
@@ -537,12 +522,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
@@ -563,12 +543,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>vBIoDoo1</t>
@@ -589,12 +564,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
@@ -615,12 +585,7 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>GlJdeJqp</t>
@@ -641,12 +606,7 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
@@ -667,12 +627,7 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>CznGurCt</t>
@@ -693,12 +648,7 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,468 +448,58 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ShJjaSDs</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>SSZaQ4Ct</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2ot8gOsJ</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KMCY9qSa</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>v5b6XwQN</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ABRGMMB5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>rPPOK0tI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>viJXIvBU</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zypxSHmo</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>rw5cZaeB</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EcDtwrdn</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>zD1kyMQb</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>EJlHkLuh</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>EqY7Orsg</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
         <is>
           <t>lnG1OUjk</t>
         </is>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t xml:space="preserve">jones r 
+  eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,12 +513,460 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>nJsvYDRG</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -461,18 +456,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
@@ -487,16 +476,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
         </is>
@@ -513,16 +496,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>vBIoDoo1</t>
         </is>
@@ -539,16 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
@@ -565,16 +536,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>GlJdeJqp</t>
         </is>
@@ -591,16 +556,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">england d 
-  eng </t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>8QQVnKh9</t>
         </is>
@@ -617,16 +576,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
         </is>
@@ -643,16 +596,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
+          <t>MeAQUqrN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>joAFj9hO</t>
         </is>
@@ -669,16 +616,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>va62Pxqi</t>
         </is>
@@ -695,278 +636,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>nJsvYDRG</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>WIs9mjGL</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>MqhPmaA4</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lb85TUOk</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rc1ER8g2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>21YvrUwq</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OGMmt88e</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EJ4unbdE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>drzevnw8</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">england d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>zil0kCo9</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ratYowuH</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,200 +453,470 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>WIs9mjGL</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>MqhPmaA4</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>lb85TUOk</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>rc1ER8g2</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>21YvrUwq</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>OGMmt88e</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>EJ4unbdE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MeAQUqrN</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>nX2mpxRQ</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>xpALVpwq</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YTzyyYmD</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>K0RAmBXI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0d4cBEPP</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HqKvGll</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0zTMbytK</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KK9ggF3s</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hY71igYg</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>CzO2kX26</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CEnSxfJ0</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -459,15 +454,14 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>
@@ -480,15 +474,14 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
@@ -501,15 +494,14 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>
@@ -522,15 +514,14 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4rSZHs2M</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
     </row>
@@ -543,13 +534,12 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
@@ -564,13 +554,12 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>GxXzVQFQ</t>
         </is>
@@ -585,15 +574,14 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
+          <t>CznGurCt</t>
         </is>
       </c>
     </row>
@@ -606,15 +594,14 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
         </is>
       </c>
     </row>
@@ -627,15 +614,14 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4fYy95jc</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
     </row>
@@ -648,275 +634,14 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>nX2mpxRQ</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>YTzyyYmD</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>K0RAmBXI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0d4cBEPP</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HqKvGll</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harrington t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0zTMbytK</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>xpALVpwq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KK9ggF3s</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>joAFj9hO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hY71igYg</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hooper s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>CzO2kX26</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith l 
-  eng </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CEnSxfJ0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>nJsvYDRG</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>lnG1OUjk</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,167 +453,175 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>hbOpz9hE</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8QQVnKh9</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>GlJdeJqp</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>4fYy95jc</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0K79iBXL</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -616,32 +629,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4fYy95jc</t>
+          <t xml:space="preserve">robinson t 
+  eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Y39YvFx6</t>
+          <t>4fYy95jc</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/england/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,12 +627,7 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>0K79iBXL</t>
@@ -662,6 +657,188 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>lAbHYaQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EubK3NNG</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Cl3y4WHa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p21q2AnC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WveT5hmm</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v3JHq2Wp</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>69B375Oi</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>A7iT11hT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
         </is>
       </c>
     </row>
